--- a/Data/Temp/3043_Latam_DataLoad_Tracker.xlsx
+++ b/Data/Temp/3043_Latam_DataLoad_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8361164-3DCA-4AB6-9A09-EB6CD500E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4E9B7D-F19B-4ED3-962B-32B71EAF16DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{53B33B9B-9600-4544-943F-760533730144}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>Revenue Validation</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>NULL Check Validation</t>
-  </si>
-  <si>
-    <t>Pivot Generation</t>
   </si>
   <si>
     <t>Overall Status</t>
@@ -247,17 +244,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63183E91-4A6E-48B6-81C6-A4A3544D0697}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -610,19 +607,18 @@
     <col min="12" max="12" width="14.140625" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" customWidth="1"/>
-    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -639,16 +635,16 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>6</v>
@@ -671,13 +667,10 @@
       <c r="P2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -692,13 +685,12 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="6"/>
-    </row>
-    <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="1"/>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -715,11 +707,10 @@
       <c r="N4" s="5"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-    </row>
-    <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -736,11 +727,10 @@
       <c r="N5" s="5"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-    </row>
-    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -757,11 +747,10 @@
       <c r="N6" s="5"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-    </row>
-    <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
@@ -778,11 +767,10 @@
       <c r="N7" s="5"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
@@ -799,11 +787,10 @@
       <c r="N8" s="5"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -820,7 +807,6 @@
       <c r="N9" s="5"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -833,7 +819,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6CB421D-3195-401C-99CD-C56A59E9F243}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -843,50 +829,49 @@
     <col min="5" max="5" width="17.140625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>11</v>
@@ -894,61 +879,94 @@
       <c r="J2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
